--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
@@ -90,12 +90,12 @@
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Ignacio</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:19</t>
+    <t xml:space="preserve">2026-09-09 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -844,7 +844,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16205</v>
+        <v>16204</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2018</v>
@@ -861,7 +861,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>16204</v>
+        <v>16205</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:15</t>
+    <t xml:space="preserve">2026-09-17 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
@@ -90,15 +90,15 @@
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:10</t>
+    <t xml:space="preserve">2026-09-23 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -844,7 +844,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16204</v>
+        <v>16108</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2018</v>
@@ -861,7 +861,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>16205</v>
+        <v>16204</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2018</v>
@@ -878,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>16108</v>
+        <v>16205</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:39</t>
+    <t xml:space="preserve">2026-10-02 13:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:42</t>
+    <t xml:space="preserve">2026-10-04 09:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:08</t>
+    <t xml:space="preserve">2026-10-05 11:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
